--- a/Data/Building/MeetingRoomTwo.Projecter001.xlsx
+++ b/Data/Building/MeetingRoomTwo.Projecter001.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H79"/>
+  <dimension ref="A1:I81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,6 +469,11 @@
           <t>actionSource</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>violationLabel</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -487,7 +492,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1709260865</v>
+        <v>1711852392</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -505,6 +510,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -523,7 +529,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1709260889</v>
+        <v>1711853029</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -538,9 +544,10 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>physical</t>
-        </is>
-      </c>
+          <t>cyber</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -559,7 +566,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1709272800</v>
+        <v>1711853075</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -577,6 +584,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -595,7 +603,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1709274076</v>
+        <v>1711854334</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -613,6 +621,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -631,7 +640,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1709252124</v>
+        <v>1711864714</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -649,6 +658,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>#10</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -667,7 +681,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1709253304</v>
+        <v>1711866373</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -685,6 +699,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -703,7 +718,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1709253367</v>
+        <v>1711942868</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -721,6 +736,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>#10</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -739,7 +759,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1709253372</v>
+        <v>1711943574</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -754,9 +774,10 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>cyber</t>
-        </is>
-      </c>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -775,7 +796,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1709339389</v>
+        <v>1712019454</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -793,6 +814,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>#10</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -811,7 +837,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1709341119</v>
+        <v>1712019697</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -829,6 +855,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -847,7 +874,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1709354022</v>
+        <v>1712105470</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -865,6 +892,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>#10</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -883,7 +915,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1709354284</v>
+        <v>1712106533</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -901,6 +933,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -919,7 +952,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1709426124</v>
+        <v>1712119387</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -937,6 +970,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>#10</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -955,7 +993,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1709427227</v>
+        <v>1712120332</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -973,6 +1011,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -991,7 +1030,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1709512280</v>
+        <v>1712120493</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1009,6 +1048,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1027,7 +1067,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1709513073</v>
+        <v>1712121733</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1045,6 +1085,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1063,7 +1104,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1709513360</v>
+        <v>1712189165</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1081,6 +1122,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>#10</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1099,7 +1145,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1709514416</v>
+        <v>1712190068</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1117,6 +1163,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1135,7 +1182,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1709526737</v>
+        <v>1712204745</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1153,6 +1200,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>#10</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1171,7 +1223,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1709528197</v>
+        <v>1712206015</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1189,6 +1241,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1207,7 +1260,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1709599417</v>
+        <v>1712276021</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1225,6 +1278,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>#10</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1243,7 +1301,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1709600786</v>
+        <v>1712277825</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1261,6 +1319,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1279,7 +1338,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1709615172</v>
+        <v>1712290831</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1297,6 +1356,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>#10</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1315,7 +1379,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>1709615408</v>
+        <v>1712290942</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1333,6 +1397,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1351,7 +1416,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1709855699</v>
+        <v>1712538182</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1369,6 +1434,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>#10</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1387,7 +1457,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1709857069</v>
+        <v>1712539399</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1405,6 +1475,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1423,7 +1494,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1709867537</v>
+        <v>1712548381</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1441,6 +1512,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>#10</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1459,7 +1535,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1709868983</v>
+        <v>1712549118</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1477,6 +1553,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1495,7 +1572,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1709944880</v>
+        <v>1712624449</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1513,6 +1590,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>#10</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1531,7 +1613,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1709946014</v>
+        <v>1712624888</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1549,6 +1631,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1567,7 +1650,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1709955192</v>
+        <v>1712636684</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1585,6 +1668,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>#10</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1603,7 +1691,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>1709956837</v>
+        <v>1712637534</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1621,6 +1709,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1639,7 +1728,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1710032523</v>
+        <v>1712722656</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -1657,6 +1746,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>#10</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1675,7 +1769,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>1710033424</v>
+        <v>1712723937</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -1693,6 +1787,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1711,7 +1806,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1710043460</v>
+        <v>1712798474</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -1729,6 +1824,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>#10</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1747,7 +1847,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1710045665</v>
+        <v>1712799258</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -1765,6 +1865,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1783,7 +1884,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1710117937</v>
+        <v>1712808066</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -1801,6 +1902,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>#10</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1819,7 +1925,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1710119587</v>
+        <v>1712808744</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -1837,6 +1943,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1855,7 +1962,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>1710463409</v>
+        <v>1712809386</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -1873,6 +1980,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>#10</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1891,7 +2003,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>1710464653</v>
+        <v>1712810592</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -1909,6 +2021,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1927,7 +2040,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>1710548843</v>
+        <v>1712883619</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -1945,6 +2058,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>#10</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1963,7 +2081,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>1710549442</v>
+        <v>1712885626</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -1981,6 +2099,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1999,7 +2118,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>1710563009</v>
+        <v>1712896097</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -2017,6 +2136,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>#10</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2035,7 +2159,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>1710564374</v>
+        <v>1712897613</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -2053,6 +2177,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2071,7 +2196,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>1710637250</v>
+        <v>1713140697</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -2089,6 +2214,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>#10</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2107,7 +2237,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>1710638667</v>
+        <v>1713141525</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -2125,6 +2255,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2143,7 +2274,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>1710650462</v>
+        <v>1713153083</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -2161,6 +2292,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>#10</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2179,7 +2315,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>1710651378</v>
+        <v>1713153696</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -2197,6 +2333,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2215,7 +2352,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1710722308</v>
+        <v>1713238184</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -2233,6 +2370,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>#10</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2251,7 +2393,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>1710723787</v>
+        <v>1713238822</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -2269,6 +2411,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2287,7 +2430,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>1710734878</v>
+        <v>1713314251</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -2305,6 +2448,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>#10</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2323,7 +2471,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>1710736406</v>
+        <v>1713315192</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -2341,6 +2489,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2359,7 +2508,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>1710808622</v>
+        <v>1713326130</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -2377,6 +2526,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2395,7 +2545,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>1710810382</v>
+        <v>1713326908</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -2413,6 +2563,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2431,7 +2582,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>1711067415</v>
+        <v>1713398089</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -2449,6 +2600,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>#10</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2467,7 +2623,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>1711068181</v>
+        <v>1713398700</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -2485,6 +2641,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2503,7 +2660,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>1711080567</v>
+        <v>1713498544</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -2521,6 +2678,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>#10</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2539,7 +2701,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>1711081043</v>
+        <v>1713499600</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -2557,6 +2719,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2575,7 +2738,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>1711081546</v>
+        <v>1713744674</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -2593,6 +2756,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>#10</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2611,7 +2779,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>1711082518</v>
+        <v>1713745869</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -2629,6 +2797,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2647,7 +2816,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>1711153978</v>
+        <v>1713754631</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -2665,6 +2834,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>#10</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2683,7 +2857,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>1711154905</v>
+        <v>1713755436</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -2701,6 +2875,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2719,7 +2894,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>1711167578</v>
+        <v>1713755503</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -2737,6 +2912,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>#10</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2755,7 +2935,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>1711169969</v>
+        <v>1713755528</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -2770,9 +2950,10 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>physical</t>
-        </is>
-      </c>
+          <t>cyber</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2791,7 +2972,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>1711239547</v>
+        <v>1713832725</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -2809,6 +2990,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2827,7 +3009,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>1711240710</v>
+        <v>1713834370</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -2845,6 +3027,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2863,7 +3046,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>1711240907</v>
+        <v>1713847129</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -2881,6 +3064,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>#10</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2899,7 +3087,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>1711241921</v>
+        <v>1713847908</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -2917,6 +3105,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2935,7 +3124,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>1711252859</v>
+        <v>1713918102</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -2953,6 +3142,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>#10</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2971,7 +3165,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>1711253325</v>
+        <v>1713918720</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -2989,6 +3183,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -3007,7 +3202,7 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>1711326329</v>
+        <v>1713931701</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -3025,6 +3220,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>#10</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -3043,7 +3243,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>1711326582</v>
+        <v>1713932839</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -3061,6 +3261,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -3079,7 +3280,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>1711338582</v>
+        <v>1714002465</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -3097,6 +3298,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>#10</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -3115,7 +3321,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>1711340395</v>
+        <v>1714003515</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -3133,6 +3339,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -3151,7 +3358,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>1711414617</v>
+        <v>1714014482</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -3169,6 +3376,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>#10</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -3187,7 +3399,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>1711415847</v>
+        <v>1714015309</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -3205,6 +3417,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -3223,7 +3436,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>1711426622</v>
+        <v>1714089514</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -3241,6 +3454,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -3259,7 +3473,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>1711427922</v>
+        <v>1714089880</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
@@ -3277,6 +3491,85 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Projecter_Operation</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>MeetingRoomTwo</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>1714101774</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>MeetingRoomTwo.Projecter001.state: on</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>#10</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Projecter_Operation</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>MeetingRoomTwo</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>1714102957</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>MeetingRoomTwo.Projecter001.state: off</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
